--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/11.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/11.xlsx
@@ -426,13 +426,13 @@
         <v>-24.1431217124897</v>
       </c>
       <c r="E2">
-        <v>-29.59459635924811</v>
+        <v>-28.49274391336079</v>
       </c>
       <c r="F2">
-        <v>-4.620943308069253</v>
+        <v>-4.377385175333821</v>
       </c>
       <c r="G2">
-        <v>-18.55702912231968</v>
+        <v>-18.62332279674359</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-23.36794057842653</v>
       </c>
       <c r="E3">
-        <v>-30.24660378263549</v>
+        <v>-28.5963055854422</v>
       </c>
       <c r="F3">
-        <v>-4.513915670450897</v>
+        <v>-4.909280725563736</v>
       </c>
       <c r="G3">
-        <v>-18.69854170194137</v>
+        <v>-18.28299540476097</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.45607756079584</v>
       </c>
       <c r="E4">
-        <v>-30.34538791463881</v>
+        <v>-29.71163703421335</v>
       </c>
       <c r="F4">
-        <v>-4.510170997813841</v>
+        <v>-4.74336456718568</v>
       </c>
       <c r="G4">
-        <v>-18.7674126360676</v>
+        <v>-17.49831665886076</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.46476456644606</v>
       </c>
       <c r="E5">
-        <v>-30.50804164404631</v>
+        <v>-28.6840402408668</v>
       </c>
       <c r="F5">
-        <v>-4.443855688163687</v>
+        <v>-4.765861901567455</v>
       </c>
       <c r="G5">
-        <v>-18.80849816148272</v>
+        <v>-17.80523899107936</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.40833153662581</v>
       </c>
       <c r="E6">
-        <v>-30.62726051500924</v>
+        <v>-29.51587110286177</v>
       </c>
       <c r="F6">
-        <v>-4.345205854838007</v>
+        <v>-4.82294658128947</v>
       </c>
       <c r="G6">
-        <v>-18.55101220580206</v>
+        <v>-17.99754692618285</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.33048848712087</v>
       </c>
       <c r="E7">
-        <v>-31.24202576815754</v>
+        <v>-29.20221087919449</v>
       </c>
       <c r="F7">
-        <v>-4.362271869782782</v>
+        <v>-4.819912992608446</v>
       </c>
       <c r="G7">
-        <v>-18.1774171416953</v>
+        <v>-17.74705946377221</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.27237461177306</v>
       </c>
       <c r="E8">
-        <v>-31.35545724933867</v>
+        <v>-30.76015084900133</v>
       </c>
       <c r="F8">
-        <v>-4.4877797717284</v>
+        <v>-4.825501098931074</v>
       </c>
       <c r="G8">
-        <v>-18.4475162758806</v>
+        <v>-17.30281570258464</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.27134056703269</v>
       </c>
       <c r="E9">
-        <v>-31.80206894139714</v>
+        <v>-29.73531189632546</v>
       </c>
       <c r="F9">
-        <v>-4.417722165000063</v>
+        <v>-4.387506639839394</v>
       </c>
       <c r="G9">
-        <v>-17.66297988343857</v>
+        <v>-17.03258083603224</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.35714186298749</v>
       </c>
       <c r="E10">
-        <v>-32.44584812751258</v>
+        <v>-30.58228144692806</v>
       </c>
       <c r="F10">
-        <v>-4.501664913342016</v>
+        <v>-4.862369772642504</v>
       </c>
       <c r="G10">
-        <v>-17.33129963640453</v>
+        <v>-17.35338263042424</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.55659208038998</v>
       </c>
       <c r="E11">
-        <v>-32.59305976055393</v>
+        <v>-31.1079285958424</v>
       </c>
       <c r="F11">
-        <v>-4.200155813748823</v>
+        <v>-4.503136967990416</v>
       </c>
       <c r="G11">
-        <v>-17.30280908149356</v>
+        <v>-17.85534409781623</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.88157443542045</v>
       </c>
       <c r="E12">
-        <v>-33.21024095458531</v>
+        <v>-33.06856764525534</v>
       </c>
       <c r="F12">
-        <v>-4.478604571507302</v>
+        <v>-4.567269930889095</v>
       </c>
       <c r="G12">
-        <v>-17.17163864613656</v>
+        <v>-15.62184813374599</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.34047784159488</v>
       </c>
       <c r="E13">
-        <v>-33.48055462505117</v>
+        <v>-32.31760174361536</v>
       </c>
       <c r="F13">
-        <v>-4.295888460778264</v>
+        <v>-4.028297590776038</v>
       </c>
       <c r="G13">
-        <v>-16.5291825918762</v>
+        <v>-15.31498870189264</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.94898667031136</v>
       </c>
       <c r="E14">
-        <v>-33.89310313562395</v>
+        <v>-33.3598979635908</v>
       </c>
       <c r="F14">
-        <v>-4.193917596147907</v>
+        <v>-4.359924817616101</v>
       </c>
       <c r="G14">
-        <v>-16.35105041277187</v>
+        <v>-15.54814711367797</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.70091771821482</v>
       </c>
       <c r="E15">
-        <v>-33.69218153661463</v>
+        <v>-33.65453406795186</v>
       </c>
       <c r="F15">
-        <v>-4.24501982677435</v>
+        <v>-4.305420786683294</v>
       </c>
       <c r="G15">
-        <v>-16.08258668808298</v>
+        <v>-15.04491108625335</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.58188966234696</v>
       </c>
       <c r="E16">
-        <v>-35.08637867901513</v>
+        <v>-34.13675541536965</v>
       </c>
       <c r="F16">
-        <v>-4.011346394510132</v>
+        <v>-4.179037095366438</v>
       </c>
       <c r="G16">
-        <v>-15.51661085687087</v>
+        <v>-14.94743041757674</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.57154903440496</v>
       </c>
       <c r="E17">
-        <v>-35.55128993453859</v>
+        <v>-34.99163394582665</v>
       </c>
       <c r="F17">
-        <v>-4.058929630592468</v>
+        <v>-4.078706950064475</v>
       </c>
       <c r="G17">
-        <v>-15.41821813289819</v>
+        <v>-14.817968223718</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.64069774148509</v>
       </c>
       <c r="E18">
-        <v>-35.85120171111858</v>
+        <v>-35.02674320480811</v>
       </c>
       <c r="F18">
-        <v>-3.936725339186456</v>
+        <v>-3.650822869536961</v>
       </c>
       <c r="G18">
-        <v>-15.50806302828847</v>
+        <v>-14.42508592129946</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.76198281817084</v>
       </c>
       <c r="E19">
-        <v>-36.59345256453081</v>
+        <v>-35.84756308225342</v>
       </c>
       <c r="F19">
-        <v>-3.79882968957027</v>
+        <v>-3.555294520570611</v>
       </c>
       <c r="G19">
-        <v>-14.94840537323806</v>
+        <v>-14.24677828328154</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.91896437704556</v>
       </c>
       <c r="E20">
-        <v>-37.27366332403796</v>
+        <v>-36.69040945727204</v>
       </c>
       <c r="F20">
-        <v>-3.756628678041555</v>
+        <v>-3.130051269657092</v>
       </c>
       <c r="G20">
-        <v>-14.77960065619062</v>
+        <v>-14.68994115135054</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.09240073004243</v>
       </c>
       <c r="E21">
-        <v>-37.35442412949075</v>
+        <v>-36.99506707461207</v>
       </c>
       <c r="F21">
-        <v>-3.386975088465876</v>
+        <v>-3.251089953509341</v>
       </c>
       <c r="G21">
-        <v>-15.00467637104182</v>
+        <v>-14.32498330055575</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.26251881439415</v>
       </c>
       <c r="E22">
-        <v>-37.98707232649534</v>
+        <v>-37.07363157017114</v>
       </c>
       <c r="F22">
-        <v>-3.249361338502638</v>
+        <v>-2.98289965081812</v>
       </c>
       <c r="G22">
-        <v>-14.86824713409569</v>
+        <v>-13.37807127050355</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.41225940263832</v>
       </c>
       <c r="E23">
-        <v>-38.16219973755697</v>
+        <v>-37.17796534707087</v>
       </c>
       <c r="F23">
-        <v>-3.189398273279312</v>
+        <v>-2.496282252710619</v>
       </c>
       <c r="G23">
-        <v>-14.46648594854081</v>
+        <v>-14.50910922235893</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-14.52516257059144</v>
       </c>
       <c r="E24">
-        <v>-38.8884492280631</v>
+        <v>-36.24633597489487</v>
       </c>
       <c r="F24">
-        <v>-3.204550379625279</v>
+        <v>-2.550220900631613</v>
       </c>
       <c r="G24">
-        <v>-14.68467572867033</v>
+        <v>-13.48391603248512</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-14.58682537145845</v>
       </c>
       <c r="E25">
-        <v>-38.86501890354741</v>
+        <v>-39.06880929084059</v>
       </c>
       <c r="F25">
-        <v>-2.720415440540229</v>
+        <v>-2.634889778135795</v>
       </c>
       <c r="G25">
-        <v>-14.26400636226791</v>
+        <v>-13.77810269601415</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-14.59418606210073</v>
       </c>
       <c r="E26">
-        <v>-38.85874470280978</v>
+        <v>-38.58642718259553</v>
       </c>
       <c r="F26">
-        <v>-2.783136529615293</v>
+        <v>-2.44176871954232</v>
       </c>
       <c r="G26">
-        <v>-14.48531302102265</v>
+        <v>-14.96587015623049</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-14.54802896994223</v>
       </c>
       <c r="E27">
-        <v>-38.8312998860863</v>
+        <v>-37.52233768145817</v>
       </c>
       <c r="F27">
-        <v>-3.006488950428591</v>
+        <v>-2.540693325844329</v>
       </c>
       <c r="G27">
-        <v>-14.71009078677531</v>
+        <v>-15.00274963353796</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-14.44676631219039</v>
       </c>
       <c r="E28">
-        <v>-38.98408607063109</v>
+        <v>-37.24637021119374</v>
       </c>
       <c r="F28">
-        <v>-2.738447516093423</v>
+        <v>-2.312532773871757</v>
       </c>
       <c r="G28">
-        <v>-15.02528948284209</v>
+        <v>-14.53939905877049</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.28997769469337</v>
       </c>
       <c r="E29">
-        <v>-38.68559170641549</v>
+        <v>-36.3241057232656</v>
       </c>
       <c r="F29">
-        <v>-2.630619315134812</v>
+        <v>-2.582050222120115</v>
       </c>
       <c r="G29">
-        <v>-14.71380687414315</v>
+        <v>-15.23892064176403</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.07781026252062</v>
       </c>
       <c r="E30">
-        <v>-38.3350266838227</v>
+        <v>-37.92583150825261</v>
       </c>
       <c r="F30">
-        <v>-2.65578598583706</v>
+        <v>-2.314228131054235</v>
       </c>
       <c r="G30">
-        <v>-14.73519796414515</v>
+        <v>-14.35027752374855</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-13.80774482237901</v>
       </c>
       <c r="E31">
-        <v>-38.02736895245259</v>
+        <v>-37.38538304204419</v>
       </c>
       <c r="F31">
-        <v>-2.661593435428977</v>
+        <v>-2.53871369345003</v>
       </c>
       <c r="G31">
-        <v>-14.78030083657218</v>
+        <v>-14.96988584796962</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-13.48268870262089</v>
       </c>
       <c r="E32">
-        <v>-38.17390584286679</v>
+        <v>-36.93216657064553</v>
       </c>
       <c r="F32">
-        <v>-2.842822446303417</v>
+        <v>-2.447844607286903</v>
       </c>
       <c r="G32">
-        <v>-15.01072970356038</v>
+        <v>-15.93720408072589</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.11478886659305</v>
       </c>
       <c r="E33">
-        <v>-37.89373821296025</v>
+        <v>-36.4905361999955</v>
       </c>
       <c r="F33">
-        <v>-2.550179724277812</v>
+        <v>-2.427801225221101</v>
       </c>
       <c r="G33">
-        <v>-14.89059993757684</v>
+        <v>-14.48380506752951</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.71034704895309</v>
       </c>
       <c r="E34">
-        <v>-37.58060329227786</v>
+        <v>-37.20887897488423</v>
       </c>
       <c r="F34">
-        <v>-2.790061283730552</v>
+        <v>-2.358011264792474</v>
       </c>
       <c r="G34">
-        <v>-15.1747109557571</v>
+        <v>-14.35364931438029</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.27634346349544</v>
       </c>
       <c r="E35">
-        <v>-37.33039151793205</v>
+        <v>-35.75566902345277</v>
       </c>
       <c r="F35">
-        <v>-2.546127020840202</v>
+        <v>-3.124615990955304</v>
       </c>
       <c r="G35">
-        <v>-15.38607770153018</v>
+        <v>-15.65430803275854</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.82055908206177</v>
       </c>
       <c r="E36">
-        <v>-36.74421225695718</v>
+        <v>-35.8101782650831</v>
       </c>
       <c r="F36">
-        <v>-2.813681465606373</v>
+        <v>-2.854937004703571</v>
       </c>
       <c r="G36">
-        <v>-15.20225303937107</v>
+        <v>-14.67685290956103</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.34849406913678</v>
       </c>
       <c r="E37">
-        <v>-36.42394046123869</v>
+        <v>-35.2147156323925</v>
       </c>
       <c r="F37">
-        <v>-2.887143248199947</v>
+        <v>-2.650866995263705</v>
       </c>
       <c r="G37">
-        <v>-15.38597176407292</v>
+        <v>-15.29881834220607</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.86728664236286</v>
       </c>
       <c r="E38">
-        <v>-36.13845640284714</v>
+        <v>-35.8830278264445</v>
       </c>
       <c r="F38">
-        <v>-2.883592579537532</v>
+        <v>-2.621409273383574</v>
       </c>
       <c r="G38">
-        <v>-15.15677110947979</v>
+        <v>-15.22422347484244</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.39308416920747</v>
       </c>
       <c r="E39">
-        <v>-35.80471466119285</v>
+        <v>-34.01731012070633</v>
       </c>
       <c r="F39">
-        <v>-2.874594754378963</v>
+        <v>-2.566636804298101</v>
       </c>
       <c r="G39">
-        <v>-15.21730443466536</v>
+        <v>-14.32568679148284</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.937796787716977</v>
       </c>
       <c r="E40">
-        <v>-35.38677500231394</v>
+        <v>-33.15150211823182</v>
       </c>
       <c r="F40">
-        <v>-2.607087820790255</v>
+        <v>-2.251752516396064</v>
       </c>
       <c r="G40">
-        <v>-15.45627947496319</v>
+        <v>-14.46536532887577</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.510523811708049</v>
       </c>
       <c r="E41">
-        <v>-34.70271730413727</v>
+        <v>-34.35265947063335</v>
       </c>
       <c r="F41">
-        <v>-2.574626600641493</v>
+        <v>-2.500688122567371</v>
       </c>
       <c r="G41">
-        <v>-15.50069209864528</v>
+        <v>-14.93737794604675</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.1189013133977</v>
       </c>
       <c r="E42">
-        <v>-35.24437034443173</v>
+        <v>-34.74641254983729</v>
       </c>
       <c r="F42">
-        <v>-2.651901947079445</v>
+        <v>-2.642721203887643</v>
       </c>
       <c r="G42">
-        <v>-15.68809049471404</v>
+        <v>-15.13788941299655</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.767162037186884</v>
       </c>
       <c r="E43">
-        <v>-34.44843443165857</v>
+        <v>-32.89772190636796</v>
       </c>
       <c r="F43">
-        <v>-2.613402056275112</v>
+        <v>-2.758258093389654</v>
       </c>
       <c r="G43">
-        <v>-15.77052638918743</v>
+        <v>-14.86809484900088</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.456563988245918</v>
       </c>
       <c r="E44">
-        <v>-33.20195384715127</v>
+        <v>-33.27444792330306</v>
       </c>
       <c r="F44">
-        <v>-2.697744690360713</v>
+        <v>-2.495077052508969</v>
       </c>
       <c r="G44">
-        <v>-15.75710874811676</v>
+        <v>-14.89465866640799</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.192907689973282</v>
       </c>
       <c r="E45">
-        <v>-32.88450102650257</v>
+        <v>-31.51447687835502</v>
       </c>
       <c r="F45">
-        <v>-2.709895673996922</v>
+        <v>-2.766717458536974</v>
       </c>
       <c r="G45">
-        <v>-15.55198238068521</v>
+        <v>-14.97873824674163</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.981301719240323</v>
       </c>
       <c r="E46">
-        <v>-32.59791428469015</v>
+        <v>-31.57713284472514</v>
       </c>
       <c r="F46">
-        <v>-2.846685105031173</v>
+        <v>-3.176130776972718</v>
       </c>
       <c r="G46">
-        <v>-15.55139806939753</v>
+        <v>-15.1390100326616</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.821216183070019</v>
       </c>
       <c r="E47">
-        <v>-32.4073696838694</v>
+        <v>-31.82868051890322</v>
       </c>
       <c r="F47">
-        <v>-2.836661830292357</v>
+        <v>-3.062453158215432</v>
       </c>
       <c r="G47">
-        <v>-15.57562464165392</v>
+        <v>-13.93016267372395</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.710403655071876</v>
       </c>
       <c r="E48">
-        <v>-32.6996713598795</v>
+        <v>-32.23317287421635</v>
       </c>
       <c r="F48">
-        <v>-2.94226334073386</v>
+        <v>-2.965733070547715</v>
       </c>
       <c r="G48">
-        <v>-15.96081654678474</v>
+        <v>-14.79641160643904</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.644379632184822</v>
       </c>
       <c r="E49">
-        <v>-31.16314427941793</v>
+        <v>-30.72025499299376</v>
       </c>
       <c r="F49">
-        <v>-2.697872970539864</v>
+        <v>-2.655860420015086</v>
       </c>
       <c r="G49">
-        <v>-15.95262625712058</v>
+        <v>-15.13898520357005</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.614804518975109</v>
       </c>
       <c r="E50">
-        <v>-30.87270380622498</v>
+        <v>-31.06518885815801</v>
       </c>
       <c r="F50">
-        <v>-2.872578696748608</v>
+        <v>-2.626034486509615</v>
       </c>
       <c r="G50">
-        <v>-15.48390432221564</v>
+        <v>-14.95807713203104</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.617175993512537</v>
       </c>
       <c r="E51">
-        <v>-31.02200533002086</v>
+        <v>-30.72626880647594</v>
       </c>
       <c r="F51">
-        <v>-2.668812758844508</v>
+        <v>-2.820386084599386</v>
       </c>
       <c r="G51">
-        <v>-15.81466258231699</v>
+        <v>-14.80573906849594</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.651072250711435</v>
       </c>
       <c r="E52">
-        <v>-30.78535633532803</v>
+        <v>-29.17764390770287</v>
       </c>
       <c r="F52">
-        <v>-2.707293645177855</v>
+        <v>-3.212892550534856</v>
       </c>
       <c r="G52">
-        <v>-15.77348105108123</v>
+        <v>-14.99884815561993</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.710995967998478</v>
       </c>
       <c r="E53">
-        <v>-30.61947833242706</v>
+        <v>-30.09550219042155</v>
       </c>
       <c r="F53">
-        <v>-2.846760331062157</v>
+        <v>-2.895953404207537</v>
       </c>
       <c r="G53">
-        <v>-16.1263272710206</v>
+        <v>-14.40825676305057</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.791179307433439</v>
       </c>
       <c r="E54">
-        <v>-30.00565273763536</v>
+        <v>-29.9183007382644</v>
       </c>
       <c r="F54">
-        <v>-2.775851482404271</v>
+        <v>-2.818972627069857</v>
       </c>
       <c r="G54">
-        <v>-15.92729396265408</v>
+        <v>-14.86691132897059</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.885594521162467</v>
       </c>
       <c r="E55">
-        <v>-29.21044817341444</v>
+        <v>-29.52895386426992</v>
       </c>
       <c r="F55">
-        <v>-2.855568903363831</v>
+        <v>-3.193968848551271</v>
       </c>
       <c r="G55">
-        <v>-15.93531375922296</v>
+        <v>-14.43023050906748</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.9843521783679</v>
       </c>
       <c r="E56">
-        <v>-29.46141846715653</v>
+        <v>-27.59598831951785</v>
       </c>
       <c r="F56">
-        <v>-3.13973721503592</v>
+        <v>-2.931577285069432</v>
       </c>
       <c r="G56">
-        <v>-15.63065418488045</v>
+        <v>-15.37460169541829</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.081895570218389</v>
       </c>
       <c r="E57">
-        <v>-28.91596150869563</v>
+        <v>-28.64278584265693</v>
       </c>
       <c r="F57">
-        <v>-2.911796798185593</v>
+        <v>-3.419673864501954</v>
       </c>
       <c r="G57">
-        <v>-16.00223147148102</v>
+        <v>-15.50182430521972</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.177414639983418</v>
       </c>
       <c r="E58">
-        <v>-28.56541686423588</v>
+        <v>-29.10477170397144</v>
       </c>
       <c r="F58">
-        <v>-3.137947627351473</v>
+        <v>-3.036226988255755</v>
       </c>
       <c r="G58">
-        <v>-16.22233640220501</v>
+        <v>-14.71066185588084</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.267890795960668</v>
       </c>
       <c r="E59">
-        <v>-28.31004262952132</v>
+        <v>-27.9116320148005</v>
       </c>
       <c r="F59">
-        <v>-3.169133964238307</v>
+        <v>-3.397585126246363</v>
       </c>
       <c r="G59">
-        <v>-16.43956446885536</v>
+        <v>-15.02112481655369</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.350014687673099</v>
       </c>
       <c r="E60">
-        <v>-27.85993948400294</v>
+        <v>-27.82010249815746</v>
       </c>
       <c r="F60">
-        <v>-3.256138807967762</v>
+        <v>-3.184718422299189</v>
       </c>
       <c r="G60">
-        <v>-16.53901987794615</v>
+        <v>-14.08020652920034</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.421180188509894</v>
       </c>
       <c r="E61">
-        <v>-28.227194197551</v>
+        <v>-26.94739762976927</v>
       </c>
       <c r="F61">
-        <v>-3.194713190331527</v>
+        <v>-2.83873410948271</v>
       </c>
       <c r="G61">
-        <v>-16.24381522166379</v>
+        <v>-14.51923618116356</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.47706621363551</v>
       </c>
       <c r="E62">
-        <v>-27.30591238848252</v>
+        <v>-28.232510626036</v>
       </c>
       <c r="F62">
-        <v>-3.378275000019409</v>
+        <v>-3.399708875878967</v>
       </c>
       <c r="G62">
-        <v>-16.35699284201486</v>
+        <v>-14.70955944421626</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.514790710353473</v>
       </c>
       <c r="E63">
-        <v>-26.67324834181891</v>
+        <v>-26.90279216079372</v>
       </c>
       <c r="F63">
-        <v>-3.163415202177655</v>
+        <v>-3.288165300842736</v>
       </c>
       <c r="G63">
-        <v>-16.23696735821581</v>
+        <v>-15.52369542432491</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.537380714017399</v>
       </c>
       <c r="E64">
-        <v>-27.34484820800047</v>
+        <v>-26.17157493430118</v>
       </c>
       <c r="F64">
-        <v>-3.329268012319094</v>
+        <v>-3.239112385670872</v>
       </c>
       <c r="G64">
-        <v>-16.31778936173881</v>
+        <v>-15.01659599025597</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.548355905585996</v>
       </c>
       <c r="E65">
-        <v>-26.49850358681093</v>
+        <v>-26.98903241979579</v>
       </c>
       <c r="F65">
-        <v>-3.434771332993839</v>
+        <v>-3.506753934262392</v>
       </c>
       <c r="G65">
-        <v>-16.50471103924991</v>
+        <v>-14.735838554707</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.549570344717461</v>
       </c>
       <c r="E66">
-        <v>-27.21388926817265</v>
+        <v>-26.61998443054069</v>
       </c>
       <c r="F66">
-        <v>-3.371869701444415</v>
+        <v>-3.567603082945407</v>
       </c>
       <c r="G66">
-        <v>-16.14122803649286</v>
+        <v>-15.42257481082787</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.542855371184153</v>
       </c>
       <c r="E67">
-        <v>-26.77769759480583</v>
+        <v>-25.94581691959678</v>
       </c>
       <c r="F67">
-        <v>-3.543025550843702</v>
+        <v>-3.664104619196794</v>
       </c>
       <c r="G67">
-        <v>-16.58289619325088</v>
+        <v>-14.54858582264197</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.528943371351613</v>
       </c>
       <c r="E68">
-        <v>-27.02969811638467</v>
+        <v>-27.16689729339506</v>
       </c>
       <c r="F68">
-        <v>-3.418202601706511</v>
+        <v>-3.745769206579387</v>
       </c>
       <c r="G68">
-        <v>-16.39162611417395</v>
+        <v>-15.08863180591774</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.50603626816225</v>
       </c>
       <c r="E69">
-        <v>-26.87257365374053</v>
+        <v>-26.72797947867562</v>
       </c>
       <c r="F69">
-        <v>-3.45465159335035</v>
+        <v>-3.556751530012816</v>
       </c>
       <c r="G69">
-        <v>-16.21783074972606</v>
+        <v>-15.37269813173321</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.477049545583863</v>
       </c>
       <c r="E70">
-        <v>-26.458399420999</v>
+        <v>-28.2130880010171</v>
       </c>
       <c r="F70">
-        <v>-3.693985982409306</v>
+        <v>-3.65128531166427</v>
       </c>
       <c r="G70">
-        <v>-16.21136525428786</v>
+        <v>-16.16605878331016</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.447432277600896</v>
       </c>
       <c r="E71">
-        <v>-27.0285931687268</v>
+        <v>-25.57433713979957</v>
       </c>
       <c r="F71">
-        <v>-3.732953858311651</v>
+        <v>-3.71976871471266</v>
       </c>
       <c r="G71">
-        <v>-16.12960305583171</v>
+        <v>-15.68231690329355</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.418871178680673</v>
       </c>
       <c r="E72">
-        <v>-27.30462177339034</v>
+        <v>-26.86919541213081</v>
       </c>
       <c r="F72">
-        <v>-3.740558022264633</v>
+        <v>-3.700097503536986</v>
       </c>
       <c r="G72">
-        <v>-15.81161522514809</v>
+        <v>-15.45580937749662</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.39232854628715</v>
       </c>
       <c r="E73">
-        <v>-27.83731522786062</v>
+        <v>-27.03073966540643</v>
       </c>
       <c r="F73">
-        <v>-3.710595890050434</v>
+        <v>-3.677254921265646</v>
       </c>
       <c r="G73">
-        <v>-15.74244634192333</v>
+        <v>-16.15586395832198</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.368104735878067</v>
       </c>
       <c r="E74">
-        <v>-27.97177014962236</v>
+        <v>-27.85475438126415</v>
       </c>
       <c r="F74">
-        <v>-3.971870940861888</v>
+        <v>-4.314008432009764</v>
       </c>
       <c r="G74">
-        <v>-16.36110453957464</v>
+        <v>-15.07178609494116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.342040625686478</v>
       </c>
       <c r="E75">
-        <v>-28.40431640141301</v>
+        <v>-27.50902803314856</v>
       </c>
       <c r="F75">
-        <v>-3.829610597742751</v>
+        <v>-3.880821312224401</v>
       </c>
       <c r="G75">
-        <v>-15.88143628584409</v>
+        <v>-14.90762276273978</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.313423768226547</v>
       </c>
       <c r="E76">
-        <v>-27.89845868391218</v>
+        <v>-26.88482317593128</v>
       </c>
       <c r="F76">
-        <v>-4.001991443667631</v>
+        <v>-4.518772896493551</v>
       </c>
       <c r="G76">
-        <v>-15.9040920042421</v>
+        <v>-15.61716702235346</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.285893402642269</v>
       </c>
       <c r="E77">
-        <v>-28.2126170397203</v>
+        <v>-27.06683613172157</v>
       </c>
       <c r="F77">
-        <v>-4.292113697728814</v>
+        <v>-3.785994544978591</v>
       </c>
       <c r="G77">
-        <v>-15.7949664916311</v>
+        <v>-14.87093364180081</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.25947144129627</v>
       </c>
       <c r="E78">
-        <v>-28.0934774170525</v>
+        <v>-28.08154488804229</v>
       </c>
       <c r="F78">
-        <v>-4.097185630685823</v>
+        <v>-3.82911093852643</v>
       </c>
       <c r="G78">
-        <v>-15.21483145714753</v>
+        <v>-15.63276796820728</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.233269275711191</v>
       </c>
       <c r="E79">
-        <v>-28.56958758879694</v>
+        <v>-28.47992380344507</v>
       </c>
       <c r="F79">
-        <v>-4.221119328951494</v>
+        <v>-4.091892093663467</v>
       </c>
       <c r="G79">
-        <v>-15.13358404852273</v>
+        <v>-15.75562893426071</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.206008182475173</v>
       </c>
       <c r="E80">
-        <v>-29.52039051992142</v>
+        <v>-28.54312318669612</v>
       </c>
       <c r="F80">
-        <v>-4.024407217194761</v>
+        <v>-4.235666459637764</v>
       </c>
       <c r="G80">
-        <v>-15.05483775705286</v>
+        <v>-14.6452256127516</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.173562396305256</v>
       </c>
       <c r="E81">
-        <v>-29.65825085413693</v>
+        <v>-29.241481805789</v>
       </c>
       <c r="F81">
-        <v>-4.178839132127008</v>
+        <v>-4.613031113315718</v>
       </c>
       <c r="G81">
-        <v>-14.83381911576003</v>
+        <v>-14.80499254047683</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.132142097111693</v>
       </c>
       <c r="E82">
-        <v>-30.70318491022184</v>
+        <v>-29.57332838107109</v>
       </c>
       <c r="F82">
-        <v>-4.416760855509391</v>
+        <v>-3.990503240957033</v>
       </c>
       <c r="G82">
-        <v>-14.87071680106798</v>
+        <v>-14.24688753128434</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.082534494317496</v>
       </c>
       <c r="E83">
-        <v>-30.6233954624437</v>
+        <v>-29.52526995066468</v>
       </c>
       <c r="F83">
-        <v>-4.416533593710526</v>
+        <v>-4.24475218047464</v>
       </c>
       <c r="G83">
-        <v>-14.84634787535341</v>
+        <v>-14.82099075179536</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.024317243191611</v>
       </c>
       <c r="E84">
-        <v>-31.14144383197317</v>
+        <v>-30.0044368423643</v>
       </c>
       <c r="F84">
-        <v>-4.536490606422529</v>
+        <v>-4.953373473808443</v>
       </c>
       <c r="G84">
-        <v>-15.32873739751723</v>
+        <v>-14.34617244727985</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.954634110763124</v>
       </c>
       <c r="E85">
-        <v>-32.59487341439399</v>
+        <v>-31.37787772415064</v>
       </c>
       <c r="F85">
-        <v>-4.552671329760574</v>
+        <v>-4.584983681553285</v>
       </c>
       <c r="G85">
-        <v>-15.14638427285032</v>
+        <v>-14.64118343664815</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.870041994309767</v>
       </c>
       <c r="E86">
-        <v>-32.51445903720279</v>
+        <v>-32.37102641572084</v>
       </c>
       <c r="F86">
-        <v>-4.567566083895282</v>
+        <v>-4.305367732535127</v>
       </c>
       <c r="G86">
-        <v>-14.93451928997359</v>
+        <v>-14.3998711511996</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.765608319138487</v>
       </c>
       <c r="E87">
-        <v>-33.50859946458067</v>
+        <v>-31.84554002763377</v>
       </c>
       <c r="F87">
-        <v>-4.672984676303551</v>
+        <v>-4.462753258999668</v>
       </c>
       <c r="G87">
-        <v>-14.75275213186713</v>
+        <v>-13.92645486271997</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.634836874045164</v>
       </c>
       <c r="E88">
-        <v>-34.67879790442876</v>
+        <v>-34.29522030632005</v>
       </c>
       <c r="F88">
-        <v>-4.405825366163282</v>
+        <v>-4.77006901633182</v>
       </c>
       <c r="G88">
-        <v>-14.78171443951745</v>
+        <v>-15.52654911457976</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.473856143354289</v>
       </c>
       <c r="E89">
-        <v>-35.14650775688897</v>
+        <v>-34.93663110052948</v>
       </c>
       <c r="F89">
-        <v>-4.753871664081663</v>
+        <v>-4.331832250235078</v>
       </c>
       <c r="G89">
-        <v>-14.53227642004275</v>
+        <v>-14.48752777598842</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.281515325276123</v>
       </c>
       <c r="E90">
-        <v>-36.9032160363145</v>
+        <v>-35.84596905940273</v>
       </c>
       <c r="F90">
-        <v>-4.650569694629379</v>
+        <v>-4.732448874163514</v>
       </c>
       <c r="G90">
-        <v>-14.92148070636717</v>
+        <v>-14.59278326086401</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.053586537320617</v>
       </c>
       <c r="E91">
-        <v>-37.66379588827277</v>
+        <v>-36.44678208413338</v>
       </c>
       <c r="F91">
-        <v>-4.836342357775215</v>
+        <v>-4.895970469197425</v>
       </c>
       <c r="G91">
-        <v>-14.49218902410771</v>
+        <v>-14.22559575764851</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.786365694630935</v>
       </c>
       <c r="E92">
-        <v>-38.58577734657543</v>
+        <v>-39.24496240126496</v>
       </c>
       <c r="F92">
-        <v>-4.729956121052612</v>
+        <v>-5.100426902880658</v>
       </c>
       <c r="G92">
-        <v>-14.92644817994884</v>
+        <v>-14.85232672059733</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.477370699003311</v>
       </c>
       <c r="E93">
-        <v>-39.95056657877011</v>
+        <v>-39.7081415154805</v>
       </c>
       <c r="F93">
-        <v>-4.783420449051932</v>
+        <v>-5.306937403136216</v>
       </c>
       <c r="G93">
-        <v>-14.57725018119375</v>
+        <v>-14.73562502451971</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.124929928021992</v>
       </c>
       <c r="E94">
-        <v>-40.77053057462798</v>
+        <v>-40.76204874281161</v>
       </c>
       <c r="F94">
-        <v>-4.737385285501938</v>
+        <v>-4.953042479272117</v>
       </c>
       <c r="G94">
-        <v>-14.35031228447671</v>
+        <v>-14.93985588938289</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.729678869417542</v>
       </c>
       <c r="E95">
-        <v>-42.5673860403685</v>
+        <v>-42.53217941919587</v>
       </c>
       <c r="F95">
-        <v>-4.890588244643804</v>
+        <v>-4.796771881772044</v>
       </c>
       <c r="G95">
-        <v>-15.51869981110615</v>
+        <v>-14.5377851678201</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.298989682763134</v>
       </c>
       <c r="E96">
-        <v>-43.09622802769525</v>
+        <v>-43.68708293808305</v>
       </c>
       <c r="F96">
-        <v>-4.839657846109187</v>
+        <v>-5.402131590154408</v>
       </c>
       <c r="G96">
-        <v>-15.30911248356043</v>
+        <v>-14.56983124864024</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.841533649169412</v>
       </c>
       <c r="E97">
-        <v>-44.91826633739244</v>
+        <v>-45.10219257345097</v>
       </c>
       <c r="F97">
-        <v>-4.924407492615056</v>
+        <v>-4.846708504844724</v>
       </c>
       <c r="G97">
-        <v>-15.11797648157784</v>
+        <v>-15.21448881568421</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.362726962374643</v>
       </c>
       <c r="E98">
-        <v>-46.68493273116083</v>
+        <v>-46.16698172382252</v>
       </c>
       <c r="F98">
-        <v>-5.151875965102581</v>
+        <v>-4.880089858130356</v>
       </c>
       <c r="G98">
-        <v>-15.49113289840064</v>
+        <v>-14.54934062702492</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.877106832407446</v>
       </c>
       <c r="E99">
-        <v>-48.66126520724735</v>
+        <v>-48.66966326229458</v>
       </c>
       <c r="F99">
-        <v>-5.221637418824732</v>
+        <v>-4.983335606022642</v>
       </c>
       <c r="G99">
-        <v>-15.50800840428707</v>
+        <v>-15.53120705215352</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.387082285604771</v>
       </c>
       <c r="E100">
-        <v>-49.96554496975155</v>
+        <v>-49.45956951192652</v>
       </c>
       <c r="F100">
-        <v>-5.312281618747866</v>
+        <v>-4.963572539903874</v>
       </c>
       <c r="G100">
-        <v>-15.81283847172486</v>
+        <v>-14.5293300345128</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.91320506811299</v>
       </c>
       <c r="E101">
-        <v>-51.44471779478748</v>
+        <v>-52.92513934653103</v>
       </c>
       <c r="F101">
-        <v>-5.288488021074304</v>
+        <v>-5.500487646032775</v>
       </c>
       <c r="G101">
-        <v>-15.89914439393366</v>
+        <v>-15.16297838236592</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.446630516263347</v>
       </c>
       <c r="E102">
-        <v>-53.24815539749815</v>
+        <v>-53.60238961615566</v>
       </c>
       <c r="F102">
-        <v>-5.340688551753104</v>
+        <v>-5.174331331277598</v>
       </c>
       <c r="G102">
-        <v>-16.206909259992</v>
+        <v>-16.66803514815708</v>
       </c>
     </row>
   </sheetData>
